--- a/BeatnotePostHotCellF1=4/AllFitsF1=4_playing with2.xlsx
+++ b/BeatnotePostHotCellF1=4/AllFitsF1=4_playing with2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCellF1=4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487E9E8B-C370-4D8E-BC7E-D089E32399E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46008F2A-7BEC-400D-9FB1-06C32AFCDEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Together" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
   <si>
     <t>Date</t>
   </si>
@@ -297,6 +297,111 @@
   </si>
   <si>
     <t>Jun29,2026+6-02-58PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-10-52AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-18-49AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-27-13AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-35-16AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-44-43AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+10-52-54AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-00-55AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-08-53AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-17-07AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-24-59AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-34-58AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-43-05AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-51-00AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+11-58-59AM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-16-28PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-24-25PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-33-26PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-41-21PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-49-13PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+12-57-07PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-05-01PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-16-18PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-24-14PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-32-36PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-40-36PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-48-48PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+1-59-58PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-13-04PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-21-04PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-33-43PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-41-36PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-49-51PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+2-57-47PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+3-19-32PM</t>
+  </si>
+  <si>
+    <t>Jul07,2026+3-59-15PM</t>
   </si>
 </sst>
 </file>
@@ -448,10 +553,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'All Together'!$B$2:$B$232</c:f>
+              <c:f>'All Together'!$B$2:$B$231</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="231"/>
+                <c:ptCount val="230"/>
                 <c:pt idx="0">
                   <c:v>10.6221259181231</c:v>
                 </c:pt>
@@ -637,16 +742,121 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>16.347944436289598</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>13.5587346114607</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>13.6287894663453</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>13.564281814943399</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>13.588373998833699</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>13.4847013836913</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>13.493443306898801</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>13.693036667407799</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>13.6672309767879</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>13.6270332177755</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>13.5711113836892</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>13.600332344222</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>13.5009743955892</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>13.597133836560999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>13.345801926629401</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>13.5152469728806</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>13.5963637628518</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>13.6061621269385</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>13.564508484015001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13.566012885219999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>13.677050331463599</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>13.697864550150999</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>13.521765815989101</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>13.5769688965988</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>13.480301532390399</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>13.457843174234499</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>13.4601858284096</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.441398970797801</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>13.4597843604533</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>13.5606966844732</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>13.566424750775999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>13.677756444678201</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>13.7089668474497</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>13.5896342791272</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>13.672859971194899</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>13.4234538610926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'All Together'!$C$2:$C$232</c:f>
+              <c:f>'All Together'!$C$2:$C$231</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="231"/>
+                <c:ptCount val="230"/>
                 <c:pt idx="0">
                   <c:v>0.171876620266287</c:v>
                 </c:pt>
@@ -832,6 +1042,111 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>0.27030866825799199</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.22233607124480101</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.222916111013889</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.21978080516705001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.21701744510815299</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.22292724198768199</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.222109442813166</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.221905259897859</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.21899661326540701</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.21885786728813</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.21579488523700499</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.220755926487161</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.22011228616490899</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.21961259407713499</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.22007796981835101</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.21807344865282799</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.22239501023331501</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.22148912103303101</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.21932862474141701</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.221461481179243</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.22005818833098301</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.218777420016466</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.22017842865582701</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.21788210076678599</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.219800999056638</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.218443725860095</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.21984807108405599</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.21905089922811899</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.220804530471746</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.22042567690074599</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.22236680616370999</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.219474041342478</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.22174008177054699</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.220246153111534</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.21859609431965099</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.22158291221496201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1890,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P232"/>
+  <dimension ref="A1:P231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
@@ -2628,180 +2943,390 @@
         <v>0.27030866825799199</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
+    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B64" s="1">
+        <v>13.5587346114607</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.22233607124480101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B65" s="1">
+        <v>13.6287894663453</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.222916111013889</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="1">
+        <v>13.564281814943399</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.21978080516705001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B67" s="1">
+        <v>13.588373998833699</v>
+      </c>
+      <c r="C67" s="1">
+        <v>0.21701744510815299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="1">
+        <v>13.4847013836913</v>
+      </c>
+      <c r="C68" s="1">
+        <v>0.22292724198768199</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" s="1">
+        <v>13.493443306898801</v>
+      </c>
+      <c r="C69" s="1">
+        <v>0.222109442813166</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="1">
+        <v>13.693036667407799</v>
+      </c>
+      <c r="C70" s="1">
+        <v>0.221905259897859</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="1">
+        <v>13.6672309767879</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.21899661326540701</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B72" s="1">
+        <v>13.6270332177755</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.21885786728813</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="1">
+        <v>13.5711113836892</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.21579488523700499</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="1">
+        <v>13.600332344222</v>
+      </c>
+      <c r="C74" s="1">
+        <v>0.220755926487161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="1">
+        <v>13.5009743955892</v>
+      </c>
+      <c r="C75" s="1">
+        <v>0.22011228616490899</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76" s="1">
+        <v>13.597133836560999</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.21961259407713499</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="1">
+        <v>13.345801926629401</v>
+      </c>
+      <c r="C77" s="1">
+        <v>0.22007796981835101</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="1">
+        <v>13.5152469728806</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.21807344865282799</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B79" s="1">
+        <v>13.5963637628518</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.22239501023331501</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" s="1">
+        <v>13.6061621269385</v>
+      </c>
+      <c r="C80" s="1">
+        <v>0.22148912103303101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B81" s="1">
+        <v>13.564508484015001</v>
+      </c>
+      <c r="C81" s="1">
+        <v>0.21932862474141701</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B82" s="1">
+        <v>13.566012885219999</v>
+      </c>
+      <c r="C82" s="1">
+        <v>0.221461481179243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83" s="1">
+        <v>13.677050331463599</v>
+      </c>
+      <c r="C83" s="1">
+        <v>0.22005818833098301</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B84" s="1">
+        <v>13.697864550150999</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0.218777420016466</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="1">
+        <v>13.521765815989101</v>
+      </c>
+      <c r="C85" s="1">
+        <v>0.22017842865582701</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B86" s="1">
+        <v>13.5769688965988</v>
+      </c>
+      <c r="C86" s="1">
+        <v>0.21788210076678599</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B87" s="1">
+        <v>13.480301532390399</v>
+      </c>
+      <c r="C87" s="1">
+        <v>0.219800999056638</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" s="1">
+        <v>13.457843174234499</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.218443725860095</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B89" s="1">
+        <v>13.4601858284096</v>
+      </c>
+      <c r="C89" s="1">
+        <v>0.21984807108405599</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" s="1">
+        <v>13.441398970797801</v>
+      </c>
+      <c r="C90" s="1">
+        <v>0.21905089922811899</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="1">
+        <v>13.4597843604533</v>
+      </c>
+      <c r="C91" s="1">
+        <v>0.220804530471746</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B92" s="1">
+        <v>13.5606966844732</v>
+      </c>
+      <c r="C92" s="1">
+        <v>0.22042567690074599</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B93" s="1">
+        <v>13.566424750775999</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.22236680616370999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" s="1">
+        <v>13.677756444678201</v>
+      </c>
+      <c r="C94" s="1">
+        <v>0.219474041342478</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B95" s="1">
+        <v>13.7089668474497</v>
+      </c>
+      <c r="C95" s="1">
+        <v>0.22174008177054699</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B96" s="1">
+        <v>13.5896342791272</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.220246153111534</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B97" s="1">
+        <v>13.672859971194899</v>
+      </c>
+      <c r="C97" s="1">
+        <v>0.21859609431965099</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B98" s="1">
+        <v>13.4234538610926</v>
+      </c>
+      <c r="C98" s="1">
+        <v>0.22158291221496201</v>
+      </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
@@ -3467,11 +3992,6 @@
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A232" s="1"/>
-      <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
